--- a/viewer/downloads/CCA2_Alignment.xlsx
+++ b/viewer/downloads/CCA2_Alignment.xlsx
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -77,6 +77,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -106,7 +111,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -119,6 +124,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -492,9 +498,9 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="55" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
-    <col width="17" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,15 +580,19 @@
           <t>9.3.6.5, 9.3.7.10, 9.3.7.2, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr">
-        <is>
-          <t>9.3.6.5 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G5" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.G.2, see ebook</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.7 (CCSS-M), 8.G.2 (CCSS-M), 9.3.6.5 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022), see ebook (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G5" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -618,15 +628,19 @@
           <t>9.3.5.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.6 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G7" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 7.SP.8a, 7.Sp.8a, 8.EE.C.7.A, see ebook</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.4a (CCSS-M), 7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.6 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), see ebook (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G7" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -662,15 +676,19 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.1, 9.3.6.4, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.6.4 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G9" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.3, 7.EE.4b, 7.SP.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.3 (CCSS-M), 7.EE.4b (CCSS-M), 7.SP.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.6.4 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G9" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -706,15 +724,19 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G11" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G11" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -750,15 +772,19 @@
           <t>9.3.5.9, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr"/>
-      <c r="F13" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.9 (MN-2022), 9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G13" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E13" s="8" t="inlineStr">
+        <is>
+          <t>8.G.C.1</t>
+        </is>
+      </c>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>8.G.C.1 (CCSS-M), 9.3.5.9 (MN-2022), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G13" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -794,15 +820,19 @@
           <t>9.3.6.5</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr"/>
-      <c r="F15" s="8" t="inlineStr">
-        <is>
-          <t>9.3.6.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G15" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E15" s="8" t="inlineStr">
+        <is>
+          <t>see ebook</t>
+        </is>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>9.3.6.5 (MN-2022), see ebook (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G15" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -833,10 +863,10 @@
           <t>7-1 w/video, 7-47, 7-71 and 7-72 with What are Radians? from 0:46 to 1:59; 7-77, 7-86 and 7-87 b and c, 7-99 and 7-100</t>
         </is>
       </c>
-      <c r="D17" s="8" t="inlineStr"/>
-      <c r="E17" s="8" t="inlineStr"/>
-      <c r="F17" s="8" t="inlineStr"/>
-      <c r="G17" s="8" t="inlineStr"/>
+      <c r="D17" s="9" t="inlineStr"/>
+      <c r="E17" s="9" t="inlineStr"/>
+      <c r="F17" s="9" t="inlineStr"/>
+      <c r="G17" s="9" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -852,10 +882,10 @@
           <t>7-114, 7-125, 7-126, 7-138, 7-143, 7-152</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr"/>
-      <c r="E18" s="8" t="inlineStr"/>
-      <c r="F18" s="8" t="inlineStr"/>
-      <c r="G18" s="8" t="inlineStr"/>
+      <c r="D18" s="9" t="inlineStr"/>
+      <c r="E18" s="9" t="inlineStr"/>
+      <c r="F18" s="9" t="inlineStr"/>
+      <c r="G18" s="9" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -889,15 +919,19 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr"/>
-      <c r="F20" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G20" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E20" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G20" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -920,15 +954,19 @@
           <t>9.2.3.7, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr"/>
-      <c r="F21" s="8" t="inlineStr">
-        <is>
-          <t>9.2.3.7 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G21" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E21" s="8" t="inlineStr">
+        <is>
+          <t>7.Sp.8a, 8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.7 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G21" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -951,15 +989,19 @@
           <t>9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr"/>
-      <c r="F22" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G22" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.B, 8.G.C.1</t>
+        </is>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.B (CCSS-M), 8.G.C.1 (CCSS-M), 9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G22" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -982,15 +1024,19 @@
           <t>9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr"/>
-      <c r="F23" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G23" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A, 8.EE.A.8</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G23" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1013,15 +1059,19 @@
           <t>9.3.5.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr"/>
-      <c r="F24" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.3 (MN-2022), 9.3.6.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G24" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E24" s="8" t="inlineStr">
+        <is>
+          <t>7.SP.8b, see ebook</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.8b (CCSS-M), 9.3.5.3 (MN-2022), 9.3.6.5 (MN-2022), see ebook (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G24" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1035,10 +1085,10 @@
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="8" t="inlineStr"/>
-      <c r="E25" s="8" t="inlineStr"/>
-      <c r="F25" s="8" t="inlineStr"/>
-      <c r="G25" s="8" t="inlineStr"/>
+      <c r="D25" s="9" t="inlineStr"/>
+      <c r="E25" s="9" t="inlineStr"/>
+      <c r="F25" s="9" t="inlineStr"/>
+      <c r="G25" s="9" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1072,15 +1122,19 @@
           <t>9.1.1.1, 9.1.1.12, 9.1.1.14, 9.1.1.15, 9.1.1.2, 9.1.1.3, 9.1.1.4, 9.1.1.5</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr"/>
-      <c r="F27" s="8" t="inlineStr">
-        <is>
-          <t>9.1.1.1 (MN-2022), 9.1.1.12 (MN-2022), 9.1.1.14 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.2 (MN-2022), 9.1.1.3 (MN-2022), 9.1.1.4 (MN-2022), 9.1.1.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G27" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>6.EE.A.2.A, 6.EE.A.2.B, 6.EE.A.3, 6.NS.B.4, 6.NS.C.6.C, 6.NS.C.7.C, MP 1, MP 7</t>
+        </is>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>6.EE.A.2.A (CCSS-M), 6.EE.A.2.B (CCSS-M), 6.EE.A.3 (CCSS-M), 6.NS.B.4 (CCSS-M), 6.NS.C.6.C (CCSS-M), 6.NS.C.7.C (CCSS-M), 9.1.1.1 (MN-2022), 9.1.1.12 (MN-2022), 9.1.1.14 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.2 (MN-2022), 9.1.1.3 (MN-2022), 9.1.1.4 (MN-2022), 9.1.1.5 (MN-2022), MP 1 (CCSS-M), MP 7 (CCSS-M)</t>
+        </is>
+      </c>
+      <c r="G27" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1103,15 +1157,19 @@
           <t>9.1.1.5</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr"/>
-      <c r="F28" s="8" t="inlineStr">
-        <is>
-          <t>9.1.1.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G28" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>6.EE.A.3</t>
+        </is>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>6.EE.A.3 (CCSS-M), 9.1.1.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G28" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1130,15 +1188,19 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr"/>
-      <c r="F29" s="8" t="inlineStr">
-        <is>
-          <t>9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G29" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
+        </is>
+      </c>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.A (CCSS-M), 6.NS.C.7.A (CCSS-M), 6.NS.C.7.B (CCSS-M), 6.NS.C.7.D (CCSS-M), 9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G29" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1165,10 +1227,10 @@
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="8" t="inlineStr"/>
-      <c r="E31" s="8" t="inlineStr"/>
-      <c r="F31" s="8" t="inlineStr"/>
-      <c r="G31" s="8" t="inlineStr"/>
+      <c r="D31" s="9" t="inlineStr"/>
+      <c r="E31" s="9" t="inlineStr"/>
+      <c r="F31" s="9" t="inlineStr"/>
+      <c r="G31" s="9" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1189,15 +1251,19 @@
           <t>9.3.7.4, 9.3.7.5, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr"/>
-      <c r="F32" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G32" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E32" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B, 8.EE.B.8, 8.G.B.1</t>
+        </is>
+      </c>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.B.4.B (CCSS-M), 8.EE.B.8 (CCSS-M), 8.G.B.1 (CCSS-M), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G32" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1216,15 +1282,19 @@
           <t>9.1.2.6, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr"/>
-      <c r="F33" s="8" t="inlineStr">
-        <is>
-          <t>9.1.2.6 (MN-2022), 9.3.7.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G33" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>8.G.B.1</t>
+        </is>
+      </c>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>8.G.B.1 (CCSS-M), 9.1.2.6 (MN-2022), 9.3.7.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G33" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1247,15 +1317,19 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr"/>
-      <c r="F34" s="8" t="inlineStr">
-        <is>
-          <t>9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G34" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>7.SP.8a</t>
+        </is>
+      </c>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>7.SP.8a (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G34" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1278,15 +1352,19 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr"/>
-      <c r="F35" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G35" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G35" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1322,15 +1400,19 @@
           <t>9.1.2.4</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr"/>
-      <c r="F37" s="8" t="inlineStr">
-        <is>
-          <t>9.1.2.4 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G37" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>6.RP.3c</t>
+        </is>
+      </c>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>6.RP.3c (CCSS-M), 9.1.2.4 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G37" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1353,15 +1435,19 @@
           <t>9.1.1.8</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr"/>
-      <c r="F38" s="8" t="inlineStr">
-        <is>
-          <t>9.1.1.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G38" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.B</t>
+        </is>
+      </c>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>6.NS.C.6.B (CCSS-M), 9.1.1.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G38" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1375,10 +1461,10 @@
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="8" t="inlineStr"/>
-      <c r="E39" s="8" t="inlineStr"/>
-      <c r="F39" s="8" t="inlineStr"/>
-      <c r="G39" s="8" t="inlineStr"/>
+      <c r="D39" s="9" t="inlineStr"/>
+      <c r="E39" s="9" t="inlineStr"/>
+      <c r="F39" s="9" t="inlineStr"/>
+      <c r="G39" s="9" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1412,15 +1498,19 @@
           <t>9.3.7.9</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr"/>
-      <c r="F41" s="8" t="inlineStr">
-        <is>
-          <t>9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G41" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E41" s="8" t="inlineStr">
+        <is>
+          <t>8.G.C.1</t>
+        </is>
+      </c>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>8.G.C.1 (CCSS-M), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G41" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>
@@ -1438,10 +1528,10 @@
           <t>So unless you really end up with time for this work, it is suggested that you prioritize other work.</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr"/>
-      <c r="E42" s="8" t="inlineStr"/>
-      <c r="F42" s="8" t="inlineStr"/>
-      <c r="G42" s="8" t="inlineStr"/>
+      <c r="D42" s="9" t="inlineStr"/>
+      <c r="E42" s="9" t="inlineStr"/>
+      <c r="F42" s="9" t="inlineStr"/>
+      <c r="G42" s="9" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -1462,15 +1552,19 @@
           <t>9.3.6.3, 9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr"/>
-      <c r="F43" s="8" t="inlineStr">
-        <is>
-          <t>9.3.6.3 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G43" s="8" t="inlineStr">
-        <is>
-          <t>mn_correlation</t>
+      <c r="E43" s="8" t="inlineStr">
+        <is>
+          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 8.EE.B.7, 8.G.2</t>
+        </is>
+      </c>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>7.EE.4a (CCSS-M), 7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.EE.B.7 (CCSS-M), 8.G.2 (CCSS-M), 9.3.6.3 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G43" s="9" t="inlineStr">
+        <is>
+          <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
       </c>
     </row>

--- a/viewer/downloads/CCA2_Alignment.xlsx
+++ b/viewer/downloads/CCA2_Alignment.xlsx
@@ -62,7 +62,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -77,11 +77,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
   </fills>
@@ -111,7 +106,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -124,7 +119,6 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -498,7 +492,7 @@
     <col width="9" customWidth="1" min="2" max="2"/>
     <col width="40" customWidth="1" min="3" max="3"/>
     <col width="55" customWidth="1" min="4" max="4"/>
-    <col width="55" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="40" customWidth="1" min="7" max="7"/>
   </cols>
@@ -580,17 +574,13 @@
           <t>9.3.6.5, 9.3.7.10, 9.3.7.2, 9.3.7.6, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8, 8.EE.B.7, 8.G.2, see ebook</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 8.EE.B.7 (CCSS-M), 8.G.2 (CCSS-M), 9.3.6.5 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022), see ebook (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G5" s="9" t="inlineStr">
+      <c r="E5" s="8" t="inlineStr"/>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.1 (MN-2007), 9.2.1.3 (MN-2007), 9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.4.1 (MN-2007), 9.3.6.5 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.6 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G5" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -628,17 +618,13 @@
           <t>9.3.5.6, 9.3.5.7, 9.3.5.8, 9.3.6.2, 9.3.6.3, 9.3.6.5, 9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 7.SP.8a, 7.Sp.8a, 8.EE.C.7.A, see ebook</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.4a (CCSS-M), 7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 7.SP.8a (CCSS-M), 7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.6 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), see ebook (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G7" s="9" t="inlineStr">
+      <c r="E7" s="8" t="inlineStr"/>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.5 (MN-2007), 9.2.1.9 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.3.7 (MN-2007), 9.2.4.1 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.2.4.8 (MN-2007), 9.3.5.6 (MN-2022), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.2 (MN-2022), 9.3.6.3 (MN-2022), 9.3.6.5 (MN-2022), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G7" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -676,17 +662,13 @@
           <t>9.3.5.7, 9.3.5.8, 9.3.6.1, 9.3.6.4, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.3, 7.EE.4b, 7.SP.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.3 (CCSS-M), 7.EE.4b (CCSS-M), 7.SP.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.6.4 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G9" s="9" t="inlineStr">
+      <c r="E9" s="8" t="inlineStr"/>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.2 (MN-2007), 9.2.3.3 (MN-2007), 9.2.3.7 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022), 9.3.6.1 (MN-2022), 9.3.6.4 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G9" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -724,17 +706,13 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G11" s="9" t="inlineStr">
+      <c r="E11" s="8" t="inlineStr"/>
+      <c r="F11" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G11" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -772,17 +750,13 @@
           <t>9.3.5.9, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E13" s="8" t="inlineStr">
-        <is>
-          <t>8.G.C.1</t>
-        </is>
-      </c>
-      <c r="F13" s="9" t="inlineStr">
-        <is>
-          <t>8.G.C.1 (CCSS-M), 9.3.5.9 (MN-2022), 9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G13" s="9" t="inlineStr">
+      <c r="E13" s="8" t="inlineStr"/>
+      <c r="F13" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.2 (MN-2007), 9.2.1.7 (MN-2007), 9.3.5.9 (MN-2022), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G13" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -820,17 +794,13 @@
           <t>9.3.6.5</t>
         </is>
       </c>
-      <c r="E15" s="8" t="inlineStr">
-        <is>
-          <t>see ebook</t>
-        </is>
-      </c>
-      <c r="F15" s="9" t="inlineStr">
-        <is>
-          <t>9.3.6.5 (MN-2022), see ebook (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G15" s="9" t="inlineStr">
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>9.2.4.1 (MN-2007), 9.3.6.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G15" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -863,10 +833,10 @@
           <t>7-1 w/video, 7-47, 7-71 and 7-72 with What are Radians? from 0:46 to 1:59; 7-77, 7-86 and 7-87 b and c, 7-99 and 7-100</t>
         </is>
       </c>
-      <c r="D17" s="9" t="inlineStr"/>
-      <c r="E17" s="9" t="inlineStr"/>
-      <c r="F17" s="9" t="inlineStr"/>
-      <c r="G17" s="9" t="inlineStr"/>
+      <c r="D17" s="8" t="inlineStr"/>
+      <c r="E17" s="8" t="inlineStr"/>
+      <c r="F17" s="8" t="inlineStr"/>
+      <c r="G17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="n">
@@ -882,10 +852,10 @@
           <t>7-114, 7-125, 7-126, 7-138, 7-143, 7-152</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr"/>
-      <c r="E18" s="9" t="inlineStr"/>
-      <c r="F18" s="9" t="inlineStr"/>
-      <c r="G18" s="9" t="inlineStr"/>
+      <c r="D18" s="8" t="inlineStr"/>
+      <c r="E18" s="8" t="inlineStr"/>
+      <c r="F18" s="8" t="inlineStr"/>
+      <c r="G18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -919,17 +889,13 @@
           <t>9.3.7.1, 9.3.7.2, 9.3.7.3</t>
         </is>
       </c>
-      <c r="E20" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 7.EE.A.1.B, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F20" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G20" s="9" t="inlineStr">
+      <c r="E20" s="8" t="inlineStr"/>
+      <c r="F20" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.9 (MN-2007), 9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G20" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -954,17 +920,13 @@
           <t>9.2.3.7, 9.3.5.6, 9.3.7.1</t>
         </is>
       </c>
-      <c r="E21" s="8" t="inlineStr">
-        <is>
-          <t>7.Sp.8a, 8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F21" s="9" t="inlineStr">
-        <is>
-          <t>7.Sp.8a (CCSS-M), 8.EE.C.7.A (CCSS-M), 9.2.3.7 (MN-2022), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G21" s="9" t="inlineStr">
+      <c r="E21" s="8" t="inlineStr"/>
+      <c r="F21" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.3.7 (MN-2022), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.2.4.8 (MN-2007), 9.3.5.6 (MN-2022), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G21" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -989,17 +951,13 @@
           <t>9.3.7.3, 9.3.7.9</t>
         </is>
       </c>
-      <c r="E22" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.B, 8.G.C.1</t>
-        </is>
-      </c>
-      <c r="F22" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.B (CCSS-M), 8.G.C.1 (CCSS-M), 9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G22" s="9" t="inlineStr">
+      <c r="E22" s="8" t="inlineStr"/>
+      <c r="F22" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.2 (MN-2007), 9.2.1.7 (MN-2007), 9.2.1.9 (MN-2007), 9.2.2.6 (MN-2007), 9.3.7.3 (MN-2022), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G22" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1024,17 +982,13 @@
           <t>9.3.7.2, 9.3.7.7</t>
         </is>
       </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A, 8.EE.A.8</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.A.1.A (CCSS-M), 8.EE.A.8 (CCSS-M), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G23" s="9" t="inlineStr">
+      <c r="E23" s="8" t="inlineStr"/>
+      <c r="F23" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.4 (MN-2007), 9.2.1.6 (MN-2007), 9.2.1.8 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.3.7.2 (MN-2022), 9.3.7.7 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1059,17 +1013,13 @@
           <t>9.3.5.3, 9.3.6.5</t>
         </is>
       </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>7.SP.8b, see ebook</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.8b (CCSS-M), 9.3.5.3 (MN-2022), 9.3.6.5 (MN-2022), see ebook (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G24" s="9" t="inlineStr">
+      <c r="E24" s="8" t="inlineStr"/>
+      <c r="F24" s="8" t="inlineStr">
+        <is>
+          <t>9.2.3.5 (MN-2007), 9.2.4.1 (MN-2007), 9.2.4.3 (MN-2007), 9.3.5.3 (MN-2022), 9.3.6.5 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G24" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1085,10 +1035,10 @@
         </is>
       </c>
       <c r="C25" s="6" t="inlineStr"/>
-      <c r="D25" s="9" t="inlineStr"/>
-      <c r="E25" s="9" t="inlineStr"/>
-      <c r="F25" s="9" t="inlineStr"/>
-      <c r="G25" s="9" t="inlineStr"/>
+      <c r="D25" s="8" t="inlineStr"/>
+      <c r="E25" s="8" t="inlineStr"/>
+      <c r="F25" s="8" t="inlineStr"/>
+      <c r="G25" s="8" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -1122,17 +1072,13 @@
           <t>9.1.1.1, 9.1.1.12, 9.1.1.14, 9.1.1.15, 9.1.1.2, 9.1.1.3, 9.1.1.4, 9.1.1.5</t>
         </is>
       </c>
-      <c r="E27" s="8" t="inlineStr">
-        <is>
-          <t>6.EE.A.2.A, 6.EE.A.2.B, 6.EE.A.3, 6.NS.B.4, 6.NS.C.6.C, 6.NS.C.7.C, MP 1, MP 7</t>
-        </is>
-      </c>
-      <c r="F27" s="9" t="inlineStr">
-        <is>
-          <t>6.EE.A.2.A (CCSS-M), 6.EE.A.2.B (CCSS-M), 6.EE.A.3 (CCSS-M), 6.NS.B.4 (CCSS-M), 6.NS.C.6.C (CCSS-M), 6.NS.C.7.C (CCSS-M), 9.1.1.1 (MN-2022), 9.1.1.12 (MN-2022), 9.1.1.14 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.2 (MN-2022), 9.1.1.3 (MN-2022), 9.1.1.4 (MN-2022), 9.1.1.5 (MN-2022), MP 1 (CCSS-M), MP 7 (CCSS-M)</t>
-        </is>
-      </c>
-      <c r="G27" s="9" t="inlineStr">
+      <c r="E27" s="8" t="inlineStr"/>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>9.1.1.1 (MN-2022), 9.1.1.12 (MN-2022), 9.1.1.14 (MN-2022), 9.1.1.15 (MN-2022), 9.1.1.2 (MN-2022), 9.1.1.3 (MN-2022), 9.1.1.4 (MN-2022), 9.1.1.5 (MN-2022), 9.4.2.1 (MN-2007), 9.4.2.2 (MN-2007), 9.4.2.3 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1157,17 +1103,13 @@
           <t>9.1.1.5</t>
         </is>
       </c>
-      <c r="E28" s="8" t="inlineStr">
-        <is>
-          <t>6.EE.A.3</t>
-        </is>
-      </c>
-      <c r="F28" s="9" t="inlineStr">
-        <is>
-          <t>6.EE.A.3 (CCSS-M), 9.1.1.5 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G28" s="9" t="inlineStr">
+      <c r="E28" s="8" t="inlineStr"/>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>9.1.1.5 (MN-2022), 9.4.2.2 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1188,17 +1130,13 @@
           <t>9.1.1.10, 9.1.1.13, 9.1.1.7, 9.1.1.9</t>
         </is>
       </c>
-      <c r="E29" s="8" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.A, 6.NS.C.7.A, 6.NS.C.7.B, 6.NS.C.7.D</t>
-        </is>
-      </c>
-      <c r="F29" s="9" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.A (CCSS-M), 6.NS.C.7.A (CCSS-M), 6.NS.C.7.B (CCSS-M), 6.NS.C.7.D (CCSS-M), 9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G29" s="9" t="inlineStr">
+      <c r="E29" s="8" t="inlineStr"/>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>9.1.1.10 (MN-2022), 9.1.1.13 (MN-2022), 9.1.1.7 (MN-2022), 9.1.1.9 (MN-2022), 9.4.1.1 (MN-2007), 9.4.1.4 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1227,10 +1165,10 @@
         </is>
       </c>
       <c r="C31" s="6" t="inlineStr"/>
-      <c r="D31" s="9" t="inlineStr"/>
-      <c r="E31" s="9" t="inlineStr"/>
-      <c r="F31" s="9" t="inlineStr"/>
-      <c r="G31" s="9" t="inlineStr"/>
+      <c r="D31" s="8" t="inlineStr"/>
+      <c r="E31" s="8" t="inlineStr"/>
+      <c r="F31" s="8" t="inlineStr"/>
+      <c r="G31" s="8" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="n">
@@ -1251,17 +1189,13 @@
           <t>9.3.7.4, 9.3.7.5, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E32" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B, 8.EE.B.8, 8.G.B.1</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.B.4.B (CCSS-M), 8.EE.B.8 (CCSS-M), 8.G.B.1 (CCSS-M), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G32" s="9" t="inlineStr">
+      <c r="E32" s="8" t="inlineStr"/>
+      <c r="F32" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.4 (MN-2007), 9.2.2.5 (MN-2007), 9.3.7.4 (MN-2022), 9.3.7.5 (MN-2022), 9.3.7.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G32" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1282,17 +1216,13 @@
           <t>9.1.2.6, 9.3.7.8</t>
         </is>
       </c>
-      <c r="E33" s="8" t="inlineStr">
-        <is>
-          <t>8.G.B.1</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="inlineStr">
-        <is>
-          <t>8.G.B.1 (CCSS-M), 9.1.2.6 (MN-2022), 9.3.7.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G33" s="9" t="inlineStr">
+      <c r="E33" s="8" t="inlineStr"/>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>9.1.2.6 (MN-2022), 9.2.2.5 (MN-2007), 9.3.7.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1317,17 +1247,13 @@
           <t>9.3.5.7, 9.3.5.8</t>
         </is>
       </c>
-      <c r="E34" s="8" t="inlineStr">
-        <is>
-          <t>7.SP.8a</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="inlineStr">
-        <is>
-          <t>7.SP.8a (CCSS-M), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G34" s="9" t="inlineStr">
+      <c r="E34" s="8" t="inlineStr"/>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>9.2.3.7 (MN-2007), 9.3.5.7 (MN-2022), 9.3.5.8 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1352,17 +1278,13 @@
           <t>9.3.7.1</t>
         </is>
       </c>
-      <c r="E35" s="8" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>8.EE.C.7.A (CCSS-M), 9.3.7.1 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G35" s="9" t="inlineStr">
+      <c r="E35" s="8" t="inlineStr"/>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>9.2.2.1 (MN-2007), 9.2.2.2 (MN-2007), 9.2.4.2 (MN-2007), 9.2.4.4 (MN-2007), 9.2.4.5 (MN-2007), 9.3.7.1 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1400,17 +1322,13 @@
           <t>9.1.2.4</t>
         </is>
       </c>
-      <c r="E37" s="8" t="inlineStr">
-        <is>
-          <t>6.RP.3c</t>
-        </is>
-      </c>
-      <c r="F37" s="9" t="inlineStr">
-        <is>
-          <t>6.RP.3c (CCSS-M), 9.1.2.4 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G37" s="9" t="inlineStr">
+      <c r="E37" s="8" t="inlineStr"/>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>9.1.2.4 (MN-2022), 9.4.3.2 (MN-2007), 9.4.3.3 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1435,17 +1353,13 @@
           <t>9.1.1.8</t>
         </is>
       </c>
-      <c r="E38" s="8" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.B</t>
-        </is>
-      </c>
-      <c r="F38" s="9" t="inlineStr">
-        <is>
-          <t>6.NS.C.6.B (CCSS-M), 9.1.1.8 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G38" s="9" t="inlineStr">
+      <c r="E38" s="8" t="inlineStr"/>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>9.1.1.8 (MN-2022), 9.4.3.4 (MN-2007)</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1461,10 +1375,10 @@
         </is>
       </c>
       <c r="C39" s="6" t="inlineStr"/>
-      <c r="D39" s="9" t="inlineStr"/>
-      <c r="E39" s="9" t="inlineStr"/>
-      <c r="F39" s="9" t="inlineStr"/>
-      <c r="G39" s="9" t="inlineStr"/>
+      <c r="D39" s="8" t="inlineStr"/>
+      <c r="E39" s="8" t="inlineStr"/>
+      <c r="F39" s="8" t="inlineStr"/>
+      <c r="G39" s="8" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
@@ -1498,17 +1412,13 @@
           <t>9.3.7.9</t>
         </is>
       </c>
-      <c r="E41" s="8" t="inlineStr">
-        <is>
-          <t>8.G.C.1</t>
-        </is>
-      </c>
-      <c r="F41" s="9" t="inlineStr">
-        <is>
-          <t>8.G.C.1 (CCSS-M), 9.3.7.9 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G41" s="9" t="inlineStr">
+      <c r="E41" s="8" t="inlineStr"/>
+      <c r="F41" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.2 (MN-2007), 9.2.1.7 (MN-2007), 9.3.7.9 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G41" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
@@ -1528,10 +1438,10 @@
           <t>So unless you really end up with time for this work, it is suggested that you prioritize other work.</t>
         </is>
       </c>
-      <c r="D42" s="9" t="inlineStr"/>
-      <c r="E42" s="9" t="inlineStr"/>
-      <c r="F42" s="9" t="inlineStr"/>
-      <c r="G42" s="9" t="inlineStr"/>
+      <c r="D42" s="8" t="inlineStr"/>
+      <c r="E42" s="8" t="inlineStr"/>
+      <c r="F42" s="8" t="inlineStr"/>
+      <c r="G42" s="8" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="4" t="n">
@@ -1552,17 +1462,13 @@
           <t>9.3.6.3, 9.3.7.10, 9.3.7.2, 9.3.7.3, 9.3.7.6</t>
         </is>
       </c>
-      <c r="E43" s="8" t="inlineStr">
-        <is>
-          <t>7.EE.4a, 7.EE.A.1.A, 7.EE.A.1.B, 8.EE.B.7, 8.G.2</t>
-        </is>
-      </c>
-      <c r="F43" s="9" t="inlineStr">
-        <is>
-          <t>7.EE.4a (CCSS-M), 7.EE.A.1.A (CCSS-M), 7.EE.A.1.B (CCSS-M), 8.EE.B.7 (CCSS-M), 8.G.2 (CCSS-M), 9.3.6.3 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022)</t>
-        </is>
-      </c>
-      <c r="G43" s="9" t="inlineStr">
+      <c r="E43" s="8" t="inlineStr"/>
+      <c r="F43" s="8" t="inlineStr">
+        <is>
+          <t>9.2.1.1 (MN-2007), 9.2.1.3 (MN-2007), 9.2.1.5 (MN-2007), 9.2.1.9 (MN-2007), 9.2.2.3 (MN-2007), 9.2.2.6 (MN-2007), 9.2.3.1 (MN-2007), 9.3.6.3 (MN-2022), 9.3.7.10 (MN-2022), 9.3.7.2 (MN-2022), 9.3.7.3 (MN-2022), 9.3.7.6 (MN-2022)</t>
+        </is>
+      </c>
+      <c r="G43" s="8" t="inlineStr">
         <is>
           <t>bridged_via_mn2022_hs, mn_correlation</t>
         </is>
